--- a/artfynd/A 43085-2026 artfynd.xlsx
+++ b/artfynd/A 43085-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>137153329</v>
       </c>
       <c r="B3" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>137153395</v>
       </c>
       <c r="B6" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43085-2026 artfynd.xlsx
+++ b/artfynd/A 43085-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>137153329</v>
       </c>
       <c r="B3" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>137153395</v>
       </c>
       <c r="B6" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43085-2026 artfynd.xlsx
+++ b/artfynd/A 43085-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>137153329</v>
       </c>
       <c r="B3" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>137153395</v>
       </c>
       <c r="B6" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43085-2026 artfynd.xlsx
+++ b/artfynd/A 43085-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>137153329</v>
       </c>
       <c r="B3" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>137153395</v>
       </c>
       <c r="B6" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43085-2026 artfynd.xlsx
+++ b/artfynd/A 43085-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>137153329</v>
       </c>
       <c r="B3" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>137153395</v>
       </c>
       <c r="B6" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43085-2026 artfynd.xlsx
+++ b/artfynd/A 43085-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>137153329</v>
       </c>
       <c r="B3" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>137153395</v>
       </c>
       <c r="B6" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43085-2026 artfynd.xlsx
+++ b/artfynd/A 43085-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>137153329</v>
       </c>
       <c r="B3" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>137153395</v>
       </c>
       <c r="B6" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
